--- a/experiment1/data_processing3/exp_data/06_trimmed.xlsx
+++ b/experiment1/data_processing3/exp_data/06_trimmed.xlsx
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>738.2692307692307</v>
+        <v>723.4400000000001</v>
       </c>
     </row>
     <row r="41">
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>717.5384615384615</v>
+        <v>693.25</v>
       </c>
     </row>
     <row r="42">
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>677.0370370370371</v>
+        <v>664.5769230769231</v>
       </c>
     </row>
     <row r="44">
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>531.52</v>
+        <v>540.4583333333334</v>
       </c>
     </row>
     <row r="63">
@@ -2829,7 +2829,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>343.1904761904762</v>
+        <v>350.55</v>
       </c>
     </row>
     <row r="135">
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>357.2592592592592</v>
+        <v>363.5</v>
       </c>
     </row>
     <row r="137">
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>383.3478260869565</v>
+        <v>371.1818181818182</v>
       </c>
     </row>
     <row r="139">
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>425.3913043478261</v>
+        <v>436.0454545454546</v>
       </c>
     </row>
     <row r="237">
